--- a/HCVData/subtyping-comparison/11-report-subtype-agreement/NS5A_CometFullSeqSubtype_4R_Subtyping_Distances.xlsx
+++ b/HCVData/subtyping-comparison/11-report-subtype-agreement/NS5A_CometFullSeqSubtype_4R_Subtyping_Distances.xlsx
@@ -431,65 +431,70 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>CometFullSeqSubtype</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>ClosestSubtypeAlignedNT</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Genotype1Distance</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Genotype2Distance</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Genotype3Distance</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Genotype4Distance</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Genotype5Distance</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Genotype6Distance</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Genotype7Distance</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Genotype8Distance</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>FirstChoiceGenotype</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>FirstChoiceDistance</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>SecondChoiceGenotype</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>SecondChoiceDistance</t>
         </is>
@@ -503,65 +508,70 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>4R</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>662</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>29.607</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>34.049</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>33.233</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>23.946</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>28.550</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>31.086</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>32.327</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>30.330</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>23.946</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>28.550</t>
         </is>
@@ -575,65 +585,70 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>4R</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>7719</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>27.930</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>31.360</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>30.675</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>23.292</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>30.738</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>28.768</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>33.001</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>30.523</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>23.292</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>27.930</t>
         </is>
@@ -647,60 +662,65 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>4R</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>347</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>22.701</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>33.429</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>32.601</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>22.636</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>28.116</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>30.199</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>30.961</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>22.701</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>22.636</t>
         </is>
@@ -714,55 +734,60 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>4R</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>332</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>24.242</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>32.628</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>25.378</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>29.167</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>30.909</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>30.605</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>24.242</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>25.378</t>
         </is>
@@ -776,55 +801,60 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>4R</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>330</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>23.030</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>30.565</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>23.867</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>28.571</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>30.000</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>30.887</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>23.030</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>23.867</t>
         </is>
@@ -838,55 +868,60 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>4R</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>330</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>23.939</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>32.482</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>23.867</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>29.483</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>30.000</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>32.110</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>23.939</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>23.867</t>
         </is>
@@ -900,50 +935,55 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>4R</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>330</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>24.169</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>35.347</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>32.593</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>23.676</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>32.121</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>24.169</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>23.676</t>
         </is>
@@ -957,55 +997,60 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>4R</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>330</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>22.727</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>31.928</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>23.263</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>29.179</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>30.303</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>30.275</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>22.727</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>23.263</t>
         </is>
@@ -1019,55 +1064,60 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>4R</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>330</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>24.242</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>32.482</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>24.773</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>29.483</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>30.303</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>32.416</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>24.242</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>24.773</t>
         </is>
@@ -1081,55 +1131,60 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>4R</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t>332</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>24.012</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>32.482</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>23.750</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>30.488</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>30.357</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>31.387</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>24.012</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>23.750</t>
         </is>
@@ -1143,55 +1198,60 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>4R</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
           <t>288</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>24.848</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>32.117</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>23.988</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>30.887</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>28.309</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>32.117</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>24.848</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>23.988</t>
         </is>
@@ -1205,55 +1265,60 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>4R</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>330</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>23.636</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>31.522</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>23.565</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>28.746</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>31.515</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>30.606</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>23.636</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>23.565</t>
         </is>
@@ -1267,60 +1332,65 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>4R</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
           <t>330</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>22.424</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>32.831</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>31.159</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>22.741</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>29.664</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>30.909</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>29.808</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>22.424</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>22.741</t>
         </is>
@@ -1334,60 +1404,65 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>4R</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
           <t>284</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>26.061</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>32.229</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>34.201</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>25.982</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>31.307</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>31.515</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>31.498</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>26.061</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>25.982</t>
         </is>
@@ -1401,60 +1476,65 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>4R</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
           <t>330</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>24.924</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>34.545</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>31.481</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>23.676</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>28.659</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>30.631</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>30.068</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>24.924</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>23.676</t>
         </is>
@@ -1468,60 +1548,65 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>4R</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
           <t>252</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>24.167</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>33.333</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>25.692</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>31.429</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>30.612</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>34.298</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>32.794</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>24.167</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>25.692</t>
         </is>
@@ -1535,60 +1620,65 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>4R</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
           <t>252</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>23.750</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>32.937</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>30.435</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>24.901</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>28.340</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>29.268</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>33.333</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>23.750</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>24.901</t>
         </is>
@@ -1615,150 +1705,155 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>CometFullSeqSubtype</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>ClosestSubtypeAlignedNT</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>AssignedGenotype</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Subtype1aDistance</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Subtype1aDistance</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Subtype1bDistance</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Subtype1bDistance</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Subtype1cDistance</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Subtype1cDistance</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Subtype1dDistance</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Subtype1eDistance</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Subtype1eDistance</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Subtype1gDistance</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Subtype1gDistance</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Subtype1hDistance</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Subtype1hDistance</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Subtype1iDistance</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Subtype1jDistance</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Subtype1kDistance</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Subtype1lDistance</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Subtype1lDistance</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Subtype1mDistance</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Subtype1mDistance</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Subtype1nDistance</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Subtype1nDistance</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Subtype1oDistance</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Subtype1oDistance</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>FirstChoiceSubtype</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>FirstChoiceDistance</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>SecondChoiceSubtype</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>SecondChoiceDistance</t>
         </is>
@@ -1772,150 +1867,155 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>4R</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>347</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>23.055</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>23.055</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>23.143</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>23.143</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>27.089</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>27.089</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>25.000</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>26.648</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>26.648</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>25.575</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>25.575</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>27.874</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>27.874</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>27.299</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>27.874</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>25.360</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>25.575</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>25.575</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>25.287</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>25.287</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>28.161</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>28.161</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>27.011</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>27.011</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1a</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>23.055</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>1b</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>23.143</t>
         </is>
@@ -1929,150 +2029,155 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>4R</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>332</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>25.152</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>25.152</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>24.096</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>24.096</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>27.576</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>27.576</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>25.994</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>24.126</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>24.126</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>24.848</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>24.848</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>23.158</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>23.158</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>26.970</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>24.561</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>24.620</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>27.576</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>27.576</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>26.061</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>26.061</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>28.485</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>28.485</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>26.061</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>26.061</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1b</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>24.096</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>1k</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>24.620</t>
         </is>
@@ -2086,150 +2191,155 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>4R</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>330</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>23.939</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>23.939</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>25.301</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>25.301</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>27.273</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>27.273</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>26.911</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>24.211</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>24.211</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>26.061</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>26.061</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>26.761</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>26.761</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>27.273</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>26.970</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>24.316</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>25.000</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>25.000</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>27.273</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>27.273</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>29.697</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>29.697</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>26.061</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>26.061</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1a</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>23.939</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>1k</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
         <is>
           <t>24.316</t>
         </is>
@@ -2243,150 +2353,155 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>4R</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>330</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>24.848</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>24.848</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>25.000</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>25.000</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>28.182</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>28.182</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>25.688</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>24.211</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>24.211</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>26.061</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>26.061</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>28.614</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>28.614</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>28.182</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>29.091</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>25.228</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>25.879</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>25.879</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>27.044</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>27.044</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>29.518</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>29.518</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>27.576</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>27.576</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1a</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>24.848</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>1b</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>25.000</t>
         </is>
@@ -2400,150 +2515,155 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>4R</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>330</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>25.152</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>25.152</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>22.535</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>22.535</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>27.070</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>27.070</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>25.714</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>25.614</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>25.614</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>25.301</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>25.301</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>27.795</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>27.795</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>26.970</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>28.485</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>25.532</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>27.157</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>27.157</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>27.273</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>27.273</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>28.788</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>28.788</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>27.273</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>27.273</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1a</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>25.152</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>1b</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
         <is>
           <t>22.535</t>
         </is>
@@ -2557,150 +2677,155 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>4R</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>330</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>23.030</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>23.030</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>24.398</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>24.398</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>27.576</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>27.576</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>25.994</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>22.456</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>22.456</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>26.970</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>26.970</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>25.602</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>25.602</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>26.970</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>25.758</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>24.316</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>25.240</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>25.240</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>26.970</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>26.970</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>28.012</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>28.012</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>24.545</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>24.545</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1a</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>23.030</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>1o</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>24.545</t>
         </is>
@@ -2714,150 +2839,155 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>4R</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>330</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>25.152</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>25.152</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>25.602</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>25.602</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>28.485</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>28.485</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>25.688</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>24.561</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>24.561</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>26.364</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>26.364</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>28.313</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>28.313</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>28.485</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>29.091</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>26.140</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>25.879</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>25.879</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>27.576</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>27.576</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>29.819</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>29.819</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>28.182</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>28.182</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1a</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>25.152</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>1b</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>25.602</t>
         </is>
@@ -2871,150 +3001,155 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>4R</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>332</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>25.228</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>25.228</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>25.982</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>25.982</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>28.115</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>28.115</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>26.415</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>24.390</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>24.390</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>26.606</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>26.606</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>26.056</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>26.056</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>29.179</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>27.964</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>24.699</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>25.559</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>25.559</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>27.052</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>27.052</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>28.875</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>28.875</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>27.660</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>27.660</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1k</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>24.699</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>1a</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>25.228</t>
         </is>
@@ -3028,150 +3163,155 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>4R</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>288</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>26.061</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>26.061</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>23.264</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>23.264</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>28.025</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>28.025</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>24.638</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>24.912</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>24.912</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>24.653</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>24.653</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>25.000</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>25.000</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>26.761</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>28.788</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>26.140</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>26.045</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>26.045</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>28.182</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>28.182</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>28.169</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Z10" t="inlineStr">
         <is>
           <t>28.169</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>28.485</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>28.485</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1b</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>23.264</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>1a</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
         <is>
           <t>26.061</t>
         </is>
@@ -3185,150 +3325,155 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>4R</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t>330</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>24.848</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>24.848</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>25.301</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>25.301</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>28.485</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>28.485</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>26.300</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>24.825</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>24.825</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>25.758</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>25.758</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>27.410</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>27.410</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>27.879</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>27.879</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>26.140</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>26.518</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>26.518</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>27.879</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>27.879</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>28.873</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>28.873</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>26.667</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>26.667</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1a</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AD11" t="inlineStr">
         <is>
           <t>24.848</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AE11" t="inlineStr">
         <is>
           <t>1b</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AF11" t="inlineStr">
         <is>
           <t>25.301</t>
         </is>
@@ -3342,150 +3487,155 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>4R</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
           <t>330</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>23.636</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>23.636</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>24.699</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>24.699</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>27.389</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>27.389</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>25.714</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>23.509</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>23.509</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>25.455</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>25.455</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>27.108</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>27.108</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>27.273</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>26.970</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>24.316</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>25.240</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>25.240</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>26.364</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>26.364</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>29.091</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>29.091</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>25.758</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>25.758</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>1a</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>23.636</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
+      <c r="AE12" t="inlineStr">
         <is>
           <t>1k</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr">
+      <c r="AF12" t="inlineStr">
         <is>
           <t>24.316</t>
         </is>
@@ -3499,150 +3649,155 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>4R</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>284</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>27.273</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>27.273</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>25.000</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>25.000</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>27.492</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>27.492</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>27.010</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>26.224</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>26.224</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>28.182</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>28.182</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>28.313</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>28.313</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>29.394</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>28.788</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>27.052</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>27.157</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>27.157</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>29.394</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>29.394</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>31.024</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>31.024</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>27.576</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>27.576</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
+      <c r="AC13" t="inlineStr">
         <is>
           <t>1b</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
+      <c r="AD13" t="inlineStr">
         <is>
           <t>25.000</t>
         </is>
       </c>
-      <c r="AD13" t="inlineStr">
+      <c r="AE13" t="inlineStr">
         <is>
           <t>1a</t>
         </is>
       </c>
-      <c r="AE13" t="inlineStr">
+      <c r="AF13" t="inlineStr">
         <is>
           <t>27.273</t>
         </is>
@@ -3656,150 +3811,155 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>4R</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
           <t>330</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>25.532</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>25.532</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>24.296</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>24.296</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>27.476</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>27.476</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>26.250</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>24.561</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>24.561</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>25.994</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>25.994</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>27.795</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>27.795</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>27.829</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>28.875</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>25.455</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>26.837</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>26.837</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>27.356</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>27.356</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>28.313</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>28.313</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
+      <c r="AA14" t="inlineStr">
         <is>
           <t>26.748</t>
         </is>
       </c>
-      <c r="AA14" t="inlineStr">
+      <c r="AB14" t="inlineStr">
         <is>
           <t>26.748</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
+      <c r="AC14" t="inlineStr">
         <is>
           <t>1k</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
+      <c r="AD14" t="inlineStr">
         <is>
           <t>25.455</t>
         </is>
       </c>
-      <c r="AD14" t="inlineStr">
+      <c r="AE14" t="inlineStr">
         <is>
           <t>1a</t>
         </is>
       </c>
-      <c r="AE14" t="inlineStr">
+      <c r="AF14" t="inlineStr">
         <is>
           <t>25.532</t>
         </is>
@@ -3813,150 +3973,155 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>4R</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
           <t>252</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>25.108</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>25.108</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>23.810</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>23.810</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>26.778</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>26.778</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>25.397</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>23.810</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>23.810</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>24.603</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>24.603</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>24.167</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>24.167</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>25.417</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>25.833</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>25.417</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>25.896</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>25.896</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>26.667</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>26.667</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>28.139</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>28.139</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
+      <c r="AA15" t="inlineStr">
         <is>
           <t>28.685</t>
         </is>
       </c>
-      <c r="AA15" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>28.685</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
+      <c r="AC15" t="inlineStr">
         <is>
           <t>1e</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
+      <c r="AD15" t="inlineStr">
         <is>
           <t>23.810</t>
         </is>
       </c>
-      <c r="AD15" t="inlineStr">
+      <c r="AE15" t="inlineStr">
         <is>
           <t>1b</t>
         </is>
       </c>
-      <c r="AE15" t="inlineStr">
+      <c r="AF15" t="inlineStr">
         <is>
           <t>23.810</t>
         </is>
@@ -3970,150 +4135,155 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>4R</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
           <t>252</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>22.944</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>22.944</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>22.619</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>22.619</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>25.523</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>25.523</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>24.603</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>25.000</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>25.000</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>25.794</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>25.794</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>25.847</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>25.847</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>23.750</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>26.407</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>25.108</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>25.896</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>25.896</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>26.339</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>26.339</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>29.167</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>29.167</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
+      <c r="AA16" t="inlineStr">
         <is>
           <t>26.190</t>
         </is>
       </c>
-      <c r="AA16" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>26.190</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
+      <c r="AC16" t="inlineStr">
         <is>
           <t>1b</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
+      <c r="AD16" t="inlineStr">
         <is>
           <t>22.619</t>
         </is>
       </c>
-      <c r="AD16" t="inlineStr">
+      <c r="AE16" t="inlineStr">
         <is>
           <t>1d</t>
         </is>
       </c>
-      <c r="AE16" t="inlineStr">
+      <c r="AF16" t="inlineStr">
         <is>
           <t>24.603</t>
         </is>
@@ -4140,145 +4310,150 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>CometFullSeqSubtype</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>ClosestSubtypeAlignedNT</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>AssignedGenotype</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Subtype2aDistance</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Subtype2aDistance</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Subtype2bDistance</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Subtype2bDistance</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Subtype2cDistance</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Subtype2dDistance</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Subtype2eDistance</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Subtype2fDistance</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Subtype2fDistance</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Subtype2iDistance</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Subtype2jDistance</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Subtype2jDistance</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Subtype2kDistance</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Subtype2lDistance</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Subtype2lDistance</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Subtype2mDistance</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Subtype2mDistance</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Subtype2qDistance</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Subtype2qDistance</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Subtype2rDistance</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Subtype2tDistance</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Subtype2uDistance</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Subtype2vDistance</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>FirstChoiceSubtype</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>FirstChoiceDistance</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>SecondChoiceSubtype</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>SecondChoiceDistance</t>
         </is>
@@ -4305,85 +4480,90 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>CometFullSeqSubtype</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>ClosestSubtypeAlignedNT</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>AssignedGenotype</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Subtype3aDistance</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Subtype3bDistance</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Subtype3dDistance</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Subtype3eDistance</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Subtype3gDistance</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Subtype3gDistance</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Subtype3hDistance</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Subtype3iDistance</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Subtype3iDistance</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Subtype3kDistance</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Subtype3kDistance</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>FirstChoiceSubtype</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>FirstChoiceDistance</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>SecondChoiceSubtype</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>SecondChoiceDistance</t>
         </is>
@@ -4410,145 +4590,150 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>CometFullSeqSubtype</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>ClosestSubtypeAlignedNT</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>AssignedGenotype</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Subtype4aDistance</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Subtype4bDistance</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Subtype4cDistance</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Subtype4dDistance</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Subtype4dDistance</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Subtype4fDistance</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Subtype4fDistance</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Subtype4gDistance</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Subtype4kDistance</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Subtype4kDistance</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Subtype4lDistance</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Subtype4mDistance</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Subtype4nDistance</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Subtype4oDistance</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Subtype4pDistance</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Subtype4qDistance</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Subtype4rDistance</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Subtype4sDistance</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Subtype4tDistance</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Subtype4vDistance</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Subtype4vDistance</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Subtype4wDistance</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Subtype4wDistance</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>FirstChoiceSubtype</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>FirstChoiceDistance</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>SecondChoiceSubtype</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>SecondChoiceDistance</t>
         </is>
@@ -4562,145 +4747,150 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>4R</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>662</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>23.946</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>23.982</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>22.308</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>21.116</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>21.116</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>21.601</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>21.601</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>19.637</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>19.486</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>19.486</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>20.274</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>22.961</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>21.382</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>24.471</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>21.903</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>19.789</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>19.637</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>24.284</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>21.719</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>19.335</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>19.335</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>22.427</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>22.427</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>4k</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>19.486</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>4v</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>19.335</t>
         </is>
@@ -4714,145 +4904,150 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>4R</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>7719</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>23.292</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>22.153</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>23.049</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>22.116</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>22.116</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>22.510</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>22.510</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>19.487</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>20.054</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>20.054</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>21.751</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>22.610</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>23.002</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>22.182</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>22.110</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>22.287</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>9.457</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>23.392</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>22.953</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>22.586</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>22.586</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>22.214</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>22.214</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>4r</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>9.457</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>19.487</t>
         </is>
@@ -4879,40 +5074,45 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>CometFullSeqSubtype</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>ClosestSubtypeAlignedNT</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>AssignedGenotype</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Subtype5aDistance</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Subtype5bDistance</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>FirstChoiceSubtype</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>FirstChoiceDistance</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>SecondChoiceSubtype</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>SecondChoiceDistance</t>
         </is>
@@ -4939,255 +5139,260 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>CometFullSeqSubtype</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>ClosestSubtypeAlignedNT</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>AssignedGenotype</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Subtype6aDistance</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Subtype6aDistance</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Subtype6bDistance</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Subtype6cDistance</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Subtype6dDistance</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Subtype6eDistance</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Subtype6fDistance</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Subtype6gDistance</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Subtype6hDistance</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Subtype6iDistance</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Subtype6jDistance</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Subtype6kDistance</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Subtype6lDistance</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Subtype6mDistance</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Subtype6nDistance</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Subtype6nDistance</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Subtype6oDistance</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Subtype6pDistance</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Subtype6qDistance</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Subtype6rDistance</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Subtype6sDistance</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Subtype6tDistance</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Subtype6tDistance</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Subtype6uDistance</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Subtype6vDistance</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Subtype6vDistance</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Subtype6wDistance</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Subtype6wDistance</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Subtype6xaDistance</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Subtype6xaDistance</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Subtype6xbDistance</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Subtype6xbDistance</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Subtype6xcDistance</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Subtype6xdDistance</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>Subtype6xdDistance</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>Subtype6xeDistance</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>Subtype6xeDistance</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>Subtype6xfDistance</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>Subtype6xfDistance</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>Subtype6xgDistance</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>Subtype6xgDistance</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>Subtype6xhDistance</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Subtype6xiDistance</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>Subtype6xiDistance</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>Subtype6xjDistance</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>FirstChoiceSubtype</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>FirstChoiceDistance</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>SecondChoiceSubtype</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>SecondChoiceDistance</t>
         </is>
@@ -5214,40 +5419,45 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>CometFullSeqSubtype</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>ClosestSubtypeAlignedNT</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>AssignedGenotype</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Subtype7aDistance</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Subtype7bDistance</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>FirstChoiceSubtype</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>FirstChoiceDistance</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>SecondChoiceSubtype</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>SecondChoiceDistance</t>
         </is>
@@ -5274,35 +5484,40 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>CometFullSeqSubtype</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>ClosestSubtypeAlignedNT</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>AssignedGenotype</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Subtype8aDistance</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>FirstChoiceSubtype</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>FirstChoiceDistance</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>SecondChoiceSubtype</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>SecondChoiceDistance</t>
         </is>

--- a/HCVData/subtyping-comparison/11-report-subtype-agreement/NS5A_CometFullSeqSubtype_4R_Subtyping_Distances.xlsx
+++ b/HCVData/subtyping-comparison/11-report-subtype-agreement/NS5A_CometFullSeqSubtype_4R_Subtyping_Distances.xlsx
@@ -9,13 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Genotype" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subtype_1" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subtype_2" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subtype_3" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subtype_4" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subtype_5" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subtype_6" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subtype_7" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subtype_8" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Subtype_4" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -580,7 +574,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MH743151</t>
+          <t>MT151222</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,74 +584,69 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>7719</t>
+          <t>347</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>27.930</t>
+          <t>22.701</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>31.360</t>
+          <t>33.429</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>30.675</t>
+          <t>32.601</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>23.292</t>
+          <t>22.636</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>30.738</t>
+          <t>28.116</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>28.768</t>
+          <t>30.199</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>33.001</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>30.523</t>
+          <t>30.961</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>22.701</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>23.292</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>27.930</t>
+          <t>22.636</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MT151222</t>
+          <t>MG000203</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -667,42 +656,37 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>332</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>22.701</t>
+          <t>24.242</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>33.429</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>32.601</t>
+          <t>32.628</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>22.636</t>
+          <t>25.378</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>28.116</t>
+          <t>29.167</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>30.199</t>
+          <t>30.909</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>30.961</t>
+          <t>30.605</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -712,7 +696,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>22.701</t>
+          <t>24.242</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -722,14 +706,14 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>22.636</t>
+          <t>25.378</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MG000203</t>
+          <t>MG000204</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -739,37 +723,37 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>330</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>24.242</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>32.628</t>
+          <t>23.030</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>30.565</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>25.378</t>
+          <t>23.867</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>29.167</t>
+          <t>28.571</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>30.909</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>30.605</t>
+          <t>30.000</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>30.887</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -779,7 +763,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>24.242</t>
+          <t>23.030</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -789,14 +773,14 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>25.378</t>
+          <t>23.867</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MG000204</t>
+          <t>MG000217</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -811,12 +795,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>23.030</t>
+          <t>23.939</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>30.565</t>
+          <t>32.482</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -826,7 +810,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>28.571</t>
+          <t>29.483</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -836,7 +820,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>30.887</t>
+          <t>32.110</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -846,7 +830,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>23.030</t>
+          <t>23.939</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -863,7 +847,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MG000217</t>
+          <t>MG000218</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -878,32 +862,27 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>23.939</t>
+          <t>24.169</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>35.347</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>32.482</t>
+          <t>32.593</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>23.867</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>29.483</t>
+          <t>23.676</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>30.000</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>32.110</t>
+          <t>32.121</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -913,7 +892,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>23.939</t>
+          <t>24.169</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -923,14 +902,14 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>23.867</t>
+          <t>23.676</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MG000218</t>
+          <t>MG000219</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -945,27 +924,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>24.169</t>
+          <t>22.727</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>35.347</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>32.593</t>
+          <t>31.928</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>23.676</t>
+          <t>23.263</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>29.179</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>32.121</t>
+          <t>30.303</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>30.275</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -975,7 +959,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>24.169</t>
+          <t>22.727</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -985,14 +969,14 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>23.676</t>
+          <t>23.263</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MG000219</t>
+          <t>MG000220</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1007,22 +991,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>22.727</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>31.928</t>
+          <t>24.242</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>32.482</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>23.263</t>
+          <t>24.773</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>29.179</t>
+          <t>29.483</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1032,7 +1016,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>30.275</t>
+          <t>32.416</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1042,7 +1026,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>22.727</t>
+          <t>24.242</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1052,14 +1036,14 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>23.263</t>
+          <t>24.773</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MG000220</t>
+          <t>MG000223</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1069,12 +1053,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>332</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>24.242</t>
+          <t>24.012</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1084,22 +1068,22 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>24.773</t>
+          <t>23.750</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>29.483</t>
+          <t>30.488</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>30.303</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>32.416</t>
+          <t>30.357</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>31.387</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1109,7 +1093,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>24.242</t>
+          <t>24.012</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1119,14 +1103,14 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>24.773</t>
+          <t>23.750</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MG000223</t>
+          <t>MG000225</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1136,37 +1120,37 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>288</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>24.012</t>
+          <t>24.848</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>32.482</t>
+          <t>32.117</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>23.750</t>
+          <t>23.988</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>30.488</t>
+          <t>30.887</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>30.357</t>
+          <t>28.309</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>31.387</t>
+          <t>32.117</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1176,7 +1160,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>24.012</t>
+          <t>24.848</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1186,14 +1170,14 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>23.750</t>
+          <t>23.988</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MG000225</t>
+          <t>MG000226</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1203,37 +1187,37 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>330</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>24.848</t>
+          <t>23.636</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>32.117</t>
+          <t>31.522</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>23.988</t>
+          <t>23.565</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>30.887</t>
+          <t>28.746</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>28.309</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>32.117</t>
+          <t>31.515</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>30.606</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1243,7 +1227,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>24.848</t>
+          <t>23.636</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1253,14 +1237,14 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>23.988</t>
+          <t>23.565</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MG000226</t>
+          <t>MG000227</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1275,32 +1259,37 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>23.636</t>
+          <t>22.424</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>32.831</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>31.522</t>
+          <t>31.159</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>23.565</t>
+          <t>22.741</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>28.746</t>
+          <t>29.664</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>31.515</t>
+          <t>30.909</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>30.606</t>
+          <t>29.808</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1310,7 +1299,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>23.636</t>
+          <t>22.424</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1320,14 +1309,14 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>23.565</t>
+          <t>22.741</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MG000227</t>
+          <t>MG000229</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1337,42 +1326,42 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>284</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>22.424</t>
+          <t>26.061</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>32.831</t>
+          <t>32.229</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>31.159</t>
+          <t>34.201</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>22.741</t>
+          <t>25.982</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>29.664</t>
+          <t>31.307</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>30.909</t>
+          <t>31.515</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>29.808</t>
+          <t>31.498</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1382,7 +1371,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>22.424</t>
+          <t>26.061</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1392,14 +1381,14 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>22.741</t>
+          <t>25.982</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MG000229</t>
+          <t>MG000234</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1409,42 +1398,42 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>330</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>26.061</t>
+          <t>24.924</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>32.229</t>
+          <t>34.545</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>34.201</t>
+          <t>31.481</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>25.982</t>
+          <t>23.676</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>31.307</t>
+          <t>28.659</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>31.515</t>
+          <t>30.631</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>31.498</t>
+          <t>30.068</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1454,7 +1443,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>26.061</t>
+          <t>24.924</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1464,14 +1453,14 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>25.982</t>
+          <t>23.676</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MG000234</t>
+          <t>KY083759</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1481,42 +1470,42 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>252</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>24.924</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>34.545</t>
+          <t>24.167</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>31.481</t>
+          <t>33.333</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>23.676</t>
+          <t>25.692</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>28.659</t>
+          <t>31.429</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>30.631</t>
+          <t>30.612</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>34.298</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>30.068</t>
+          <t>32.794</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1526,7 +1515,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>24.924</t>
+          <t>24.167</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1536,14 +1525,14 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>23.676</t>
+          <t>25.692</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>KY083759</t>
+          <t>KY083760</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1558,39 +1547,39 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>24.167</t>
+          <t>23.750</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>32.937</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
+          <t>30.435</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>24.901</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>28.340</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>29.268</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
           <t>33.333</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>25.692</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>31.429</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>30.612</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>34.298</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>32.794</t>
-        </is>
-      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>1</t>
@@ -1598,7 +1587,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>24.167</t>
+          <t>23.750</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1607,78 +1596,6 @@
         </is>
       </c>
       <c r="O17" t="inlineStr">
-        <is>
-          <t>25.692</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>KY083760</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>4R</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>252</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>23.750</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>32.937</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>30.435</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>24.901</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>28.340</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>29.268</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>33.333</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>23.750</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
         <is>
           <t>24.901</t>
         </is>
@@ -4325,286 +4242,6 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Subtype2aDistance</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Subtype2aDistance</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Subtype2bDistance</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Subtype2bDistance</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Subtype2cDistance</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Subtype2dDistance</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Subtype2eDistance</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Subtype2fDistance</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Subtype2fDistance</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Subtype2iDistance</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>Subtype2jDistance</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>Subtype2jDistance</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>Subtype2kDistance</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>Subtype2lDistance</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>Subtype2lDistance</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>Subtype2mDistance</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Subtype2mDistance</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>Subtype2qDistance</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>Subtype2qDistance</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>Subtype2rDistance</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>Subtype2tDistance</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>Subtype2uDistance</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>Subtype2vDistance</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>FirstChoiceSubtype</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>FirstChoiceDistance</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>SecondChoiceSubtype</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>SecondChoiceDistance</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Accession</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>CometFullSeqSubtype</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>ClosestSubtypeAlignedNT</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>AssignedGenotype</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Subtype3aDistance</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Subtype3bDistance</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Subtype3dDistance</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Subtype3eDistance</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Subtype3gDistance</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Subtype3gDistance</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Subtype3hDistance</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Subtype3iDistance</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Subtype3iDistance</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Subtype3kDistance</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>Subtype3kDistance</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>FirstChoiceSubtype</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>FirstChoiceDistance</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>SecondChoiceSubtype</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>SecondChoiceDistance</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Accession</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>CometFullSeqSubtype</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>ClosestSubtypeAlignedNT</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>AssignedGenotype</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
           <t>Subtype4aDistance</t>
         </is>
       </c>
@@ -4893,633 +4530,6 @@
       <c r="AE2" t="inlineStr">
         <is>
           <t>19.335</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>MH743151</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>4R</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>7719</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>23.292</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>22.153</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>23.049</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>22.116</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>22.116</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>22.510</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>22.510</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>19.487</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>20.054</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>20.054</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>21.751</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>22.610</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>23.002</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>22.182</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>22.110</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>22.287</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>9.457</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>23.392</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>22.953</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>22.586</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>22.586</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>22.214</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>22.214</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>4r</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>9.457</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>4g</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>19.487</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Accession</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>CometFullSeqSubtype</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>ClosestSubtypeAlignedNT</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>AssignedGenotype</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Subtype5aDistance</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Subtype5bDistance</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>FirstChoiceSubtype</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>FirstChoiceDistance</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>SecondChoiceSubtype</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>SecondChoiceDistance</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Accession</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>CometFullSeqSubtype</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>ClosestSubtypeAlignedNT</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>AssignedGenotype</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Subtype6aDistance</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Subtype6aDistance</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Subtype6bDistance</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Subtype6cDistance</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Subtype6dDistance</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Subtype6eDistance</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Subtype6fDistance</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Subtype6gDistance</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Subtype6hDistance</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Subtype6iDistance</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>Subtype6jDistance</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>Subtype6kDistance</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>Subtype6lDistance</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>Subtype6mDistance</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>Subtype6nDistance</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>Subtype6nDistance</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Subtype6oDistance</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>Subtype6pDistance</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>Subtype6qDistance</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>Subtype6rDistance</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>Subtype6sDistance</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>Subtype6tDistance</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>Subtype6tDistance</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>Subtype6uDistance</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>Subtype6vDistance</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>Subtype6vDistance</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>Subtype6wDistance</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>Subtype6wDistance</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>Subtype6xaDistance</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>Subtype6xaDistance</t>
-        </is>
-      </c>
-      <c r="AI1" t="inlineStr">
-        <is>
-          <t>Subtype6xbDistance</t>
-        </is>
-      </c>
-      <c r="AJ1" t="inlineStr">
-        <is>
-          <t>Subtype6xbDistance</t>
-        </is>
-      </c>
-      <c r="AK1" t="inlineStr">
-        <is>
-          <t>Subtype6xcDistance</t>
-        </is>
-      </c>
-      <c r="AL1" t="inlineStr">
-        <is>
-          <t>Subtype6xdDistance</t>
-        </is>
-      </c>
-      <c r="AM1" t="inlineStr">
-        <is>
-          <t>Subtype6xdDistance</t>
-        </is>
-      </c>
-      <c r="AN1" t="inlineStr">
-        <is>
-          <t>Subtype6xeDistance</t>
-        </is>
-      </c>
-      <c r="AO1" t="inlineStr">
-        <is>
-          <t>Subtype6xeDistance</t>
-        </is>
-      </c>
-      <c r="AP1" t="inlineStr">
-        <is>
-          <t>Subtype6xfDistance</t>
-        </is>
-      </c>
-      <c r="AQ1" t="inlineStr">
-        <is>
-          <t>Subtype6xfDistance</t>
-        </is>
-      </c>
-      <c r="AR1" t="inlineStr">
-        <is>
-          <t>Subtype6xgDistance</t>
-        </is>
-      </c>
-      <c r="AS1" t="inlineStr">
-        <is>
-          <t>Subtype6xgDistance</t>
-        </is>
-      </c>
-      <c r="AT1" t="inlineStr">
-        <is>
-          <t>Subtype6xhDistance</t>
-        </is>
-      </c>
-      <c r="AU1" t="inlineStr">
-        <is>
-          <t>Subtype6xiDistance</t>
-        </is>
-      </c>
-      <c r="AV1" t="inlineStr">
-        <is>
-          <t>Subtype6xiDistance</t>
-        </is>
-      </c>
-      <c r="AW1" t="inlineStr">
-        <is>
-          <t>Subtype6xjDistance</t>
-        </is>
-      </c>
-      <c r="AX1" t="inlineStr">
-        <is>
-          <t>FirstChoiceSubtype</t>
-        </is>
-      </c>
-      <c r="AY1" t="inlineStr">
-        <is>
-          <t>FirstChoiceDistance</t>
-        </is>
-      </c>
-      <c r="AZ1" t="inlineStr">
-        <is>
-          <t>SecondChoiceSubtype</t>
-        </is>
-      </c>
-      <c r="BA1" t="inlineStr">
-        <is>
-          <t>SecondChoiceDistance</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Accession</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>CometFullSeqSubtype</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>ClosestSubtypeAlignedNT</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>AssignedGenotype</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Subtype7aDistance</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Subtype7bDistance</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>FirstChoiceSubtype</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>FirstChoiceDistance</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>SecondChoiceSubtype</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>SecondChoiceDistance</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Accession</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>CometFullSeqSubtype</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>ClosestSubtypeAlignedNT</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>AssignedGenotype</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Subtype8aDistance</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>FirstChoiceSubtype</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>FirstChoiceDistance</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>SecondChoiceSubtype</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>SecondChoiceDistance</t>
         </is>
       </c>
     </row>
